--- a/Job1_Section_Placements_GR12_2026_27.xlsx
+++ b/Job1_Section_Placements_GR12_2026_27.xlsx
@@ -6403,7 +6403,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -13968,16 +13968,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -13987,16 +13987,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>26</v>
@@ -14028,13 +14028,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -14044,16 +14044,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -14063,16 +14063,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -14082,16 +14082,16 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>75/160</t>
+          <t>71/160</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -16110,7 +16110,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Job1_Section_Placements_GR12_2026_27.xlsx
+++ b/Job1_Section_Placements_GR12_2026_27.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -13904,16 +13904,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -13923,16 +13923,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -13942,16 +13942,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -13961,13 +13961,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>16</v>
@@ -13980,16 +13980,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -13999,16 +13999,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>7</v>
@@ -14027,7 +14027,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>64/160</t>
+          <t>62/160</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
